--- a/experiment_results/wu_calibration/rtt_bursts_rps10_att4_WU200000.xlsx
+++ b/experiment_results/wu_calibration/rtt_bursts_rps10_att4_WU200000.xlsx
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:010.2</t>
+          <t>00:009.7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>296</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.1</t>
+          <t>00:020.2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>505.0</t>
+          <t>532.6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>622.6</t>
+          <t>579.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>104.09</t>
+          <t>100.85</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>427869</t>
+          <t>442891</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,22 +590,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:031.5</t>
+          <t>00:027.2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1058.8</t>
+          <t>1022.8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>516.1</t>
+          <t>498.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1826107</t>
+          <t>1086042</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:039.3</t>
+          <t>00:041.1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1176.0</t>
+          <t>1127.4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>479.4</t>
+          <t>583.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3559021</t>
+          <t>1512911</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.5</t>
+          <t>00:049.8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1130.4</t>
+          <t>555.7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>527.2</t>
+          <t>644.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5089620</t>
+          <t>1753351</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,22 +766,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1038.7</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>606.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6614447</t>
+          <t>1784017</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.4</t>
+          <t>01:010.8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>633.8</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>613.1</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7575793</t>
+          <t>1860038</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:019.9</t>
+          <t>01:020.9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>262.1</t>
+          <t>263.4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>219.5</t>
+          <t>211.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7960696</t>
+          <t>2002703</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.1</t>
+          <t>01:030.0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>210.1</t>
+          <t>206.6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>211.2</t>
+          <t>192.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8260489</t>
+          <t>2131844</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,22 +994,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>178.9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>177.3</t>
+          <t>117.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8571243</t>
+          <t>2245904</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.9</t>
+          <t>01:049.6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>189.9</t>
+          <t>166.3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>175.2</t>
+          <t>120.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8832187</t>
+          <t>2345768</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:059.9</t>
+          <t>02:000.0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>160.1</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>196.6</t>
+          <t>118.4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9043781</t>
+          <t>2430955</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:009.9</t>
+          <t>02:010.1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>178.6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>193.1</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9239920</t>
+          <t>2534946</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.9</t>
+          <t>02:020.1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>118.8</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>132.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9382517</t>
+          <t>2654135</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:029.9</t>
+          <t>02:029.7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>134.4</t>
+          <t>188.8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>117.7</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9547857</t>
+          <t>2759451</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:038.4</t>
+          <t>02:036.0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>115.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9625423</t>
+          <t>2796215</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:049.4</t>
+          <t>02:050.4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>9622543</t>
+          <t>2796369</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1450,22 +1450,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>9619070</t>
+          <t>2796452</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
